--- a/research/traditional_assets/database/data/oman/oman_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_insurance_life.xlsx
@@ -587,116 +587,119 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.157</v>
+      </c>
+      <c r="E2">
+        <v>-0.154</v>
+      </c>
       <c r="G2">
-        <v>0.1501547987616099</v>
+        <v>0.05962762196559038</v>
       </c>
       <c r="H2">
-        <v>0.1501547987616099</v>
+        <v>0.05962762196559038</v>
       </c>
       <c r="I2">
-        <v>0.07647058823529411</v>
+        <v>0.03511666273862833</v>
       </c>
       <c r="J2">
-        <v>0.06547010607521697</v>
+        <v>0.02795397835463827</v>
       </c>
       <c r="K2">
-        <v>20.9</v>
+        <v>10</v>
       </c>
       <c r="L2">
-        <v>0.06470588235294117</v>
+        <v>0.02356823002592505</v>
       </c>
       <c r="M2">
-        <v>24.1</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.1027280477408355</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.15311004784689</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>24.1</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.1027280477408355</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1.15311004784689</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>18.9</v>
+        <v>129.8</v>
       </c>
       <c r="V2">
-        <v>0.08056265984654731</v>
+        <v>0.3689596361569074</v>
       </c>
       <c r="W2">
-        <v>0.1247761194029851</v>
+        <v>0.05875440658049354</v>
       </c>
       <c r="X2">
-        <v>0.09261631724381178</v>
+        <v>0.1728742536208168</v>
       </c>
       <c r="Y2">
-        <v>0.03215980215917329</v>
+        <v>-0.1141198470403233</v>
       </c>
       <c r="Z2">
-        <v>2.198774676650783</v>
+        <v>2.666708566400604</v>
       </c>
       <c r="AA2">
-        <v>0.1439540113158277</v>
+        <v>0.07454511354329092</v>
       </c>
       <c r="AB2">
-        <v>0.09111048936597135</v>
+        <v>0.1435432149338335</v>
       </c>
       <c r="AC2">
-        <v>0.05284352194985631</v>
+        <v>-0.06899810139054262</v>
       </c>
       <c r="AD2">
-        <v>7.81</v>
+        <v>156.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7.81</v>
+        <v>156.5</v>
       </c>
       <c r="AG2">
-        <v>-11.09</v>
+        <v>26.69999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.03221814281589043</v>
+        <v>0.3078890419043872</v>
       </c>
       <c r="AI2">
-        <v>0.04387393966631088</v>
+        <v>0.287050623624358</v>
       </c>
       <c r="AJ2">
-        <v>-0.04961746678000985</v>
+        <v>0.07054161162483484</v>
       </c>
       <c r="AK2">
-        <v>-0.06970020740368299</v>
+        <v>0.06427539720751081</v>
       </c>
       <c r="AL2">
-        <v>0.185</v>
+        <v>2.23</v>
       </c>
       <c r="AM2">
-        <v>0.185</v>
+        <v>2.23</v>
       </c>
       <c r="AN2">
-        <v>0.285036496350365</v>
+        <v>8.413978494623656</v>
       </c>
       <c r="AO2">
-        <v>133.5135135135135</v>
+        <v>6.681614349775785</v>
       </c>
       <c r="AP2">
-        <v>-0.4047445255474453</v>
+        <v>1.435483870967741</v>
       </c>
       <c r="AQ2">
-        <v>133.5135135135135</v>
+        <v>6.681614349775785</v>
       </c>
     </row>
     <row r="3">
@@ -715,116 +718,119 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.157</v>
+      </c>
+      <c r="E3">
+        <v>-0.154</v>
+      </c>
       <c r="G3">
-        <v>0.1501547987616099</v>
+        <v>0.05962762196559038</v>
       </c>
       <c r="H3">
-        <v>0.1501547987616099</v>
+        <v>0.05962762196559038</v>
       </c>
       <c r="I3">
-        <v>0.07647058823529411</v>
+        <v>0.03511666273862833</v>
       </c>
       <c r="J3">
-        <v>0.06547010607521697</v>
+        <v>0.02795397835463827</v>
       </c>
       <c r="K3">
-        <v>20.9</v>
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>0.06470588235294117</v>
+        <v>0.02356823002592505</v>
       </c>
       <c r="M3">
-        <v>24.1</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1027280477408355</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>1.15311004784689</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>24.1</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.1027280477408355</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>1.15311004784689</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>18.9</v>
+        <v>129.8</v>
       </c>
       <c r="V3">
-        <v>0.08056265984654731</v>
+        <v>0.3689596361569074</v>
       </c>
       <c r="W3">
-        <v>0.1247761194029851</v>
+        <v>0.05875440658049354</v>
       </c>
       <c r="X3">
-        <v>0.09261631724381178</v>
+        <v>0.1728742536208168</v>
       </c>
       <c r="Y3">
-        <v>0.03215980215917329</v>
+        <v>-0.1141198470403233</v>
       </c>
       <c r="Z3">
-        <v>2.198774676650783</v>
+        <v>2.666708566400604</v>
       </c>
       <c r="AA3">
-        <v>0.1439540113158277</v>
+        <v>0.07454511354329092</v>
       </c>
       <c r="AB3">
-        <v>0.09111048936597135</v>
+        <v>0.1435432149338335</v>
       </c>
       <c r="AC3">
-        <v>0.05284352194985631</v>
+        <v>-0.06899810139054262</v>
       </c>
       <c r="AD3">
-        <v>7.81</v>
+        <v>156.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7.81</v>
+        <v>156.5</v>
       </c>
       <c r="AG3">
-        <v>-11.09</v>
+        <v>26.69999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.03221814281589043</v>
+        <v>0.3078890419043872</v>
       </c>
       <c r="AI3">
-        <v>0.04387393966631088</v>
+        <v>0.287050623624358</v>
       </c>
       <c r="AJ3">
-        <v>-0.04961746678000985</v>
+        <v>0.07054161162483484</v>
       </c>
       <c r="AK3">
-        <v>-0.06970020740368299</v>
+        <v>0.06427539720751081</v>
       </c>
       <c r="AL3">
-        <v>0.185</v>
+        <v>2.23</v>
       </c>
       <c r="AM3">
-        <v>0.185</v>
+        <v>2.23</v>
       </c>
       <c r="AN3">
-        <v>0.285036496350365</v>
+        <v>8.413978494623656</v>
       </c>
       <c r="AO3">
-        <v>133.5135135135135</v>
+        <v>6.681614349775785</v>
       </c>
       <c r="AP3">
-        <v>-0.4047445255474453</v>
+        <v>1.435483870967741</v>
       </c>
       <c r="AQ3">
-        <v>133.5135135135135</v>
+        <v>6.681614349775785</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/oman/oman_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_insurance_life.xlsx
@@ -588,118 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.157</v>
-      </c>
-      <c r="E2">
-        <v>-0.154</v>
+        <v>0.244</v>
       </c>
       <c r="G2">
-        <v>0.05962762196559038</v>
+        <v>0.02853360788351228</v>
       </c>
       <c r="H2">
-        <v>0.05962762196559038</v>
+        <v>0.02853360788351228</v>
       </c>
       <c r="I2">
-        <v>0.03511666273862833</v>
+        <v>0.008015884688924842</v>
       </c>
       <c r="J2">
-        <v>0.02795397835463827</v>
+        <v>0.008015884688924842</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>-5.29</v>
       </c>
       <c r="L2">
-        <v>0.02356823002592505</v>
+        <v>-0.00778055596411237</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.03914795624640184</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-2.570888468809074</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.03914795624640184</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-2.570888468809074</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>129.8</v>
+        <v>106.4</v>
       </c>
       <c r="V2">
-        <v>0.3689596361569074</v>
+        <v>0.3062751871042027</v>
       </c>
       <c r="W2">
-        <v>0.05875440658049354</v>
+        <v>-0.02980281690140845</v>
       </c>
       <c r="X2">
-        <v>0.1728742536208168</v>
+        <v>0.1354442487229169</v>
       </c>
       <c r="Y2">
-        <v>-0.1141198470403233</v>
+        <v>-0.1652470656243254</v>
       </c>
       <c r="Z2">
-        <v>2.666708566400604</v>
+        <v>3.392714570858283</v>
       </c>
       <c r="AA2">
-        <v>0.07454511354329092</v>
+        <v>0.02719560878243513</v>
       </c>
       <c r="AB2">
-        <v>0.1435432149338335</v>
+        <v>0.1079493928904866</v>
       </c>
       <c r="AC2">
-        <v>-0.06899810139054262</v>
+        <v>-0.08075378410805149</v>
       </c>
       <c r="AD2">
-        <v>156.5</v>
+        <v>205.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>156.5</v>
+        <v>205.5</v>
       </c>
       <c r="AG2">
-        <v>26.69999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.3078890419043872</v>
+        <v>0.3716766142159523</v>
       </c>
       <c r="AI2">
-        <v>0.287050623624358</v>
+        <v>0.3762358110582204</v>
       </c>
       <c r="AJ2">
-        <v>0.07054161162483484</v>
+        <v>0.2219484882418813</v>
       </c>
       <c r="AK2">
-        <v>0.06427539720751081</v>
+        <v>0.2253296953160528</v>
       </c>
       <c r="AL2">
-        <v>2.23</v>
+        <v>9.35</v>
       </c>
       <c r="AM2">
-        <v>2.23</v>
+        <v>9.35</v>
       </c>
       <c r="AN2">
-        <v>8.413978494623656</v>
+        <v>16.44</v>
       </c>
       <c r="AO2">
-        <v>6.681614349775785</v>
+        <v>0.5828877005347594</v>
       </c>
       <c r="AP2">
-        <v>1.435483870967741</v>
+        <v>7.928</v>
       </c>
       <c r="AQ2">
-        <v>6.681614349775785</v>
+        <v>0.5828877005347594</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Life and General Insurance Company SAOG (MSM:NLIF)</t>
+          <t>Liva Group SAOG (MSM:LIVA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,118 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.157</v>
-      </c>
-      <c r="E3">
-        <v>-0.154</v>
+        <v>0.244</v>
       </c>
       <c r="G3">
-        <v>0.05962762196559038</v>
+        <v>0.02853360788351228</v>
       </c>
       <c r="H3">
-        <v>0.05962762196559038</v>
+        <v>0.02853360788351228</v>
       </c>
       <c r="I3">
-        <v>0.03511666273862833</v>
+        <v>0.008015884688924842</v>
       </c>
       <c r="J3">
-        <v>0.02795397835463827</v>
+        <v>0.008015884688924842</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>-5.29</v>
       </c>
       <c r="L3">
-        <v>0.02356823002592505</v>
+        <v>-0.00778055596411237</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>13.6</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03914795624640184</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>-2.570888468809074</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>13.6</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03914795624640184</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>-2.570888468809074</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>129.8</v>
+        <v>106.4</v>
       </c>
       <c r="V3">
-        <v>0.3689596361569074</v>
+        <v>0.3062751871042027</v>
       </c>
       <c r="W3">
-        <v>0.05875440658049354</v>
+        <v>-0.02980281690140845</v>
       </c>
       <c r="X3">
-        <v>0.1728742536208168</v>
+        <v>0.1354442487229169</v>
       </c>
       <c r="Y3">
-        <v>-0.1141198470403233</v>
+        <v>-0.1652470656243254</v>
       </c>
       <c r="Z3">
-        <v>2.666708566400604</v>
+        <v>3.392714570858283</v>
       </c>
       <c r="AA3">
-        <v>0.07454511354329092</v>
+        <v>0.02719560878243513</v>
       </c>
       <c r="AB3">
-        <v>0.1435432149338335</v>
+        <v>0.1079493928904866</v>
       </c>
       <c r="AC3">
-        <v>-0.06899810139054262</v>
+        <v>-0.08075378410805149</v>
       </c>
       <c r="AD3">
-        <v>156.5</v>
+        <v>205.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>156.5</v>
+        <v>205.5</v>
       </c>
       <c r="AG3">
-        <v>26.69999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.3078890419043872</v>
+        <v>0.3716766142159523</v>
       </c>
       <c r="AI3">
-        <v>0.287050623624358</v>
+        <v>0.3762358110582204</v>
       </c>
       <c r="AJ3">
-        <v>0.07054161162483484</v>
+        <v>0.2219484882418813</v>
       </c>
       <c r="AK3">
-        <v>0.06427539720751081</v>
+        <v>0.2253296953160528</v>
       </c>
       <c r="AL3">
-        <v>2.23</v>
+        <v>9.35</v>
       </c>
       <c r="AM3">
-        <v>2.23</v>
+        <v>9.35</v>
       </c>
       <c r="AN3">
-        <v>8.413978494623656</v>
+        <v>16.44</v>
       </c>
       <c r="AO3">
-        <v>6.681614349775785</v>
+        <v>0.5828877005347594</v>
       </c>
       <c r="AP3">
-        <v>1.435483870967741</v>
+        <v>7.928</v>
       </c>
       <c r="AQ3">
-        <v>6.681614349775785</v>
+        <v>0.5828877005347594</v>
       </c>
     </row>
   </sheetData>
